--- a/docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="1. Ce que l'outil utilise" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="2. Si on change une version" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="3. Ce qui a été testé" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="3. Tests à réaliser" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="4. Procédure de montée" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="5. Relevé des postes" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Annexe — modules Python" sheetId="7" state="visible" r:id="rId9"/>
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="276">
   <si>
     <t xml:space="preserve">VISU PTBG 1.0.0 — versions et dépendances</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce classeur dit de quoi l'outil a besoin pour fonctionner, ce qui a été testé, et ce qu'il faut vérifier avant de changer une version (requis REQ_COMMON_KH_3004).</t>
+    <t xml:space="preserve">Ce classeur dit de quoi l'outil a besoin pour fonctionner, ce qui reste à tester, et ce qu'il faut vérifier avant de changer une version (requis REQ_COMMON_KH_3004).</t>
   </si>
   <si>
     <t xml:space="preserve">En une phrase</t>
@@ -76,10 +76,10 @@
     <t xml:space="preserve">Les cas prévisibles (nouveau Python, nouvelle bibliothèque, autre système…) : ce qui se passe et ce qu'il faut faire, avec un feu vert / orange / rouge.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Ce qui a été testé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaque combinaison de versions sur laquelle l'outil a été essayé, et le résultat.</t>
+    <t xml:space="preserve">3. Tests à réaliser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Où lancer les tests (poste Windows, VM Linux), ce qui est déjà constaté, ce qui reste à faire.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Procédure de montée</t>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">VERT</t>
   </si>
   <si>
-    <t xml:space="preserve">Rien à faire : identique, ou déjà testé et validé.</t>
+    <t xml:space="preserve">Rien à changer : identique, ou compatible avec les versions de référence.</t>
   </si>
   <si>
     <t xml:space="preserve">ORANGE</t>
@@ -172,10 +172,10 @@
     <t xml:space="preserve">Écarts entre le PC Spyder et la référence</t>
   </si>
   <si>
-    <t xml:space="preserve">Configurations essayées</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dont en échec</t>
+    <t xml:space="preserve">Postes à tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont tests encore à lancer</t>
   </si>
   <si>
     <t xml:space="preserve">De quoi l'outil a-t-il besoin, en quelle version, et qu'est-ce qui risque de casser si on change cette version ?</t>
@@ -424,7 +424,7 @@
     <t xml:space="preserve">Toutes ces versions existent pour Windows 11 64 bits et pour SLES 15 SP7 64 bits (fichiers d'installation vérifiés, sans compilation). Le 32 bits n'est pas une cible du projet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Le PC Spyder n'a pas les versions de référence (on ne peut rien y installer), mais ses versions exactes ont passé les 145 tests : voir l'onglet 3.</t>
+    <t xml:space="preserve">Le PC Spyder n'a pas les versions de référence (on ne peut rien y installer) ; l'outil s'y lance. Les tests automatiques diront si ces versions conviennent : voir l'onglet 3.</t>
   </si>
   <si>
     <t xml:space="preserve">Que se passe-t-il si on passe à une autre version de Python, d'une bibliothèque ou de système, et que faut-il faire ?</t>
@@ -445,10 +445,10 @@
     <t xml:space="preserve">Passer de Python 3.11 à 3.12, 3.13 ou 3.14</t>
   </si>
   <si>
-    <t xml:space="preserve">Les versions figées de numpy et matplotlib existent pour ces Python. Rien à changer dans l'outil ni dans requirements.txt. Déjà testé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refaire les tests sur le poste (onglet 4).</t>
+    <t xml:space="preserve">Les versions figées de numpy et matplotlib existent pour ces Python. Rien à changer dans l'outil ni dans requirements.txt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lancer les tests sur le poste (onglet 4).</t>
   </si>
   <si>
     <t xml:space="preserve">Passer à Python 3.15</t>
@@ -463,10 +463,10 @@
     <t xml:space="preserve">Revenir à Python 3.10</t>
   </si>
   <si>
-    <t xml:space="preserve">Le code fonctionne (testé), mais numpy doit redescendre en 2.2 au maximum (numpy 2.3 et plus exigent Python 3.11) et contourpy en 1.3.2 au maximum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adapter requirements.txt et refaire les tests.</t>
+    <t xml:space="preserve">Le code est écrit pour Python 3.10, mais numpy doit redescendre en 2.2 au maximum (numpy 2.3 et plus exigent Python 3.11) et contourpy en 1.3.2 au maximum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adapter requirements.txt et lancer les tests.</t>
   </si>
   <si>
     <t xml:space="preserve">Rester en Python 3.6 (texte du requis REQ 3001)</t>
@@ -481,19 +481,19 @@
     <t xml:space="preserve">Monter numpy en 2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">numpy 2.5 exige Python 3.12 ou plus : impossible en restant en Python 3.11. Avec Python 3.12 ou plus, l'outil fonctionne (testé avec numpy 2.5.4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monter d'abord Python (ligne 1).</t>
+    <t xml:space="preserve">numpy 2.5 exige Python 3.12 ou plus : impossible en restant en Python 3.11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monter d'abord Python (ligne 1), puis lancer les tests.</t>
   </si>
   <si>
     <t xml:space="preserve">Monter matplotlib en 3.11</t>
   </si>
   <si>
-    <t xml:space="preserve">Fonctionne (testé avec matplotlib 3.11.2). matplotlib 3.11 ne supporte plus Python 3.10.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refaire les tests.</t>
+    <t xml:space="preserve">Version compatible avec Python 3.11 ; elle ne supporte plus Python 3.10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lancer les tests avant de l'adopter.</t>
   </si>
   <si>
     <t xml:space="preserve">Monter contourpy en 1.4</t>
@@ -517,19 +517,19 @@
     <t xml:space="preserve">Le PC Spyder garde numpy 2.2.0 et matplotlib 3.9.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Fonctionne : ces versions exactes ont passé les 145 tests, et l'outil a été lancé sur le PC avec un fichier du projet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rien.</t>
+    <t xml:space="preserve">L'outil s'y lance et ouvre un fichier du projet. Ces versions acceptent Python 3.11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lancer les tests sur le PC pour le confirmer (onglet 3).</t>
   </si>
   <si>
     <t xml:space="preserve">Le PC Spyder passe aux versions de référence (numpy 2.4.6, matplotlib 3.10.9)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce sont les versions de référence : testées.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rien (ou relancer les tests pour s'en assurer).</t>
+    <t xml:space="preserve">Ce sont les versions de référence (requirements.txt).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lancer les tests sur le PC.</t>
   </si>
   <si>
     <t xml:space="preserve">Utiliser Tk 9 (certains Python récents)</t>
@@ -547,247 +547,175 @@
     <t xml:space="preserve">Mêmes sources, mêmes versions figées. Les bibliothèques compilées existent dans les deux versions (Windows et Linux). SLES doit avoir glibc 2.28 ou plus (SP7 a 2.38).</t>
   </si>
   <si>
-    <t xml:space="preserve">Pas encore essayé sur le vrai Service Unit SLES : faire l'essai de réception de 15 minutes et lancer les tests sur le poste (docs/COMPATIBILITE_OS.md § 5).</t>
+    <t xml:space="preserve">À faire sur la VM Linux SLES 15 SP7 fournie par l'entreprise : installer, lancer les tests et faire l'essai de réception de 15 minutes (docs/COMPATIBILITE_OS.md § 5).</t>
   </si>
   <si>
     <t xml:space="preserve">Passer en 32 bits</t>
   </si>
   <si>
-    <t xml:space="preserve">Non prévu : les cibles sont en 64 bits, et le 32 bits n'est ni ciblé ni testé (certaines bibliothèques n'existent même pas en 32 bits).</t>
+    <t xml:space="preserve">Non prévu : les cibles sont en 64 bits, le 32 bits n'est pas une cible du projet (certaines bibliothèques n'existent même pas en 32 bits).</t>
   </si>
   <si>
     <t xml:space="preserve">Rester en 64 bits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sur quelles combinaisons de versions l'outil a-t-il été essayé, et avec quel résultat ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configuration</t>
+    <t xml:space="preserve">Où faut-il lancer les tests automatiques (145 tests fournis avec l'outil), qu'est-ce qui est déjà constaté, et qu'est-ce qui reste à faire ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poste</t>
   </si>
   <si>
     <t xml:space="preserve">Tk</t>
   </si>
   <si>
-    <t xml:space="preserve">Résultat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. PC Windows 11 / Spyder 6 (le vrai poste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outil lancé, fichier CSV du projet ouvert sans problème.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERT — OK</t>
+    <t xml:space="preserve">État</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment faire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. PC Windows 11 / Spyder 6 (poste de l'alternance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À FAIRE — l'outil se lance et ouvre un fichier du projet (30/10/2026) ; les tests restent à lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la console Spyder : import sys, puis %cd &lt;dossier de l'outil&gt;, puis !"{sys.executable}" -m unittest discover -s tests -v. Résultat attendu : « OK » à la fin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. VM Linux SLES 15 SP7 fournie par l'entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À FAIRE — quand la VM sera disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installer (install/installer_sles.sh), lancer python -m unittest discover -s tests -v, puis l'essai de réception de 15 minutes (docs/COMPATIBILITE_OS.md § 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Avant toute montée de version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nouvelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À FAIRE — à chaque montée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suivre l'onglet 4 (procédure de montée).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les tests vérifient tout l'outil : lecture des CSV (y compris abîmés), base de temps, curseurs, graphiques, rapport PDF, projet, et les vraies fenêtres de l'interface (des fenêtres s'ouvrent et se ferment pendant les tests, c'est normal).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une fois un test fait : remplacer « À FAIRE » par « VERT — OK » (ou « ROUGE — échec » avec le détail) et reporter les versions dans l'onglet 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que faut-il faire, dans l'ordre, avant d'adopter une nouvelle version ? (remplir les cases jaunes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Étape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quoi faire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment (commande ou document)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fait le</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résultat / remarque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regarder dans l'onglet 2 si le cas est déjà connu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lire les notes de version des bibliothèques changées (ce qui est supprimé ou modifié, versions de Python acceptées).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site pypi.org de chaque bibliothèque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérifier que les fichiers d'installation existent pour Windows 11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">python -m pip download --only-binary=:all: --platform win_amd64 --python-version 3.11 -r requirements.txt -d wheels_win</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérifier que les fichiers d'installation existent pour SLES 15 SP7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Même commande avec --platform manylinux2014_x86_64 --platform manylinux_2_28_x86_64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installer les nouvelles versions dans un environnement neuf et relever les versions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">python tools/audit_environnement.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lancer tous les tests : aucun échec accepté.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">python -m unittest discover -s tests -v   (dans la console Spyder : %cd &lt;dossier de l'outil&gt; puis !"{sys.executable}" -m unittest discover -s tests -v, après import sys)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesurer la vitesse sur de vrais fichiers PTBG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">python tools/banc_performance.py fichiers.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faire l'essai de réception de 15 minutes sur chaque poste (PC Windows, VM Linux SLES 15 SP7 fournie par l'entreprise).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/COMPATIBILITE_OS.md § 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mettre à jour requirements.txt, docs/DEPENDANCES.md, CHANGELOG.md et ce classeur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelles versions trouve-t-on sur chaque poste ? (une colonne par poste ; orange = différent de la référence, ce qui n'est pas forcément un problème : les tests le diront)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Référence (requirements.txt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC Windows 11 / Spyder 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VM Linux SLES 15 SP7 fournie par l'entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autre poste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Système</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows 11 ou SLES 15 SP7 (64 bits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows 11 (10.0.26100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tcl/Tk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résultat de l'essai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outil lancé, fichier du projet ouvert : OK ; tests à lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date du relevé</t>
   </si>
   <si>
     <t xml:space="preserve">30/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Banc Linux Ubuntu 24.04 avec les versions du PC Spyder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145 tests sur 145, fenêtres comprises.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Banc Linux Ubuntu 24.04 avec les versions du PC Spyder, Python 3.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145 tests sur 145 (les 20 tests de fenêtres ne se lancent pas avec Tk 9 ; le PC a Tk 8.6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Banc Linux Ubuntu 24.04, versions de référence (requirements.txt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145 tests sur 145.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Banc Linux Ubuntu 24.04, versions de référence, Tk 8.6 comme Windows et SLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Banc Linux Ubuntu 24.04, versions les plus anciennes acceptées</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145 tests sur 145 (les 20 tests de fenêtres ne se lancent pas : matplotlib 3.6 avec Tk 9).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Banc Linux Ubuntu 24.04 pendant le développement (py311-mpl39-tk9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suite de l'époque (131 tests) réussie, 12 tests de fenêtres non lancés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Banc Linux Ubuntu 24.04 pendant le développement (py312-old-tk86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suite de l'époque (131 tests) réussie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Banc Linux Ubuntu 24.04 pendant le développement (py313-ref-tk9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Banc Linux Ubuntu 24.04 pendant le développement (py314-latest-tk9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les tests vérifient tout l'outil : lecture des CSV (y compris abîmés), base de temps, curseurs, graphiques, rapport PDF, projet, et les vraies fenêtres de l'interface.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le banc Linux est un Ubuntu 24.04 (64 bits), pas le Service Unit SLES 15 SP7 : il montre que le code tourne sous Linux, mais l'essai sur le vrai SLES reste à faire (onglet 4, étape 8). Pour Windows, les tests automatiques restent à lancer sur le PC (voir onglet 4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Que faut-il faire, dans l'ordre, avant d'adopter une nouvelle version ? (remplir les cases jaunes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Étape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quoi faire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment (commande ou document)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fait le</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Par</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résultat / remarque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regarder dans l'onglet 2 si le cas est déjà connu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lire les notes de version des bibliothèques changées (ce qui est supprimé ou modifié, versions de Python acceptées).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site pypi.org de chaque bibliothèque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vérifier que les fichiers d'installation existent pour Windows 11.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">python -m pip download --only-binary=:all: --platform win_amd64 --python-version 3.11 -r requirements.txt -d wheels_win</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vérifier que les fichiers d'installation existent pour SLES 15 SP7.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Même commande avec --platform manylinux2014_x86_64 --platform manylinux_2_28_x86_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installer les nouvelles versions dans un environnement neuf et relever les versions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">python tools/audit_environnement.py</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lancer tous les tests : aucun échec accepté.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">python -m unittest discover -s tests -v   (dans la console Spyder : %cd &lt;dossier de l'outil&gt; puis !"{sys.executable}" -m unittest discover -s tests -v, après import sys)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesurer la vitesse sur de vrais fichiers PTBG.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">python tools/banc_performance.py fichiers.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faire l'essai de réception de 15 minutes sur chaque poste.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docs/COMPATIBILITE_OS.md § 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mettre à jour requirements.txt, docs/DEPENDANCES.md, CHANGELOG.md et ce classeur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quelles versions trouve-t-on sur chaque poste ? (une colonne par poste ; orange = différent de la référence, ce qui n'est pas forcément un problème : voir l'onglet 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Référence (requirements.txt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC Windows 11 / Spyder 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Unit SLES 15 SP7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autre poste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Système</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows 11 ou SLES 15 SP7 (64 bits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows 11 (10.0.26100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tcl/Tk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résultat de l'essai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145 tests sur 145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outil lancé, fichier du projet ouvert : OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date du relevé</t>
   </si>
   <si>
     <t xml:space="preserve">Pour remplir une colonne : dans l'outil, menu Information &gt; Sources, partie « Environnement d'exécution et bibliothèques » (ou lancer python tools/audit_environnement.py).</t>
@@ -1663,8 +1591,8 @@
         <v>48</v>
       </c>
       <c r="B38" s="10" t="n">
-        <f aca="false">COUNTA('3. Ce qui a été testé'!G5:G40)</f>
-        <v>10</v>
+        <f aca="false">COUNTA('3. Tests à réaliser'!A5:A6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1672,8 +1600,8 @@
         <v>49</v>
       </c>
       <c r="B39" s="10" t="n">
-        <f aca="false">COUNTIF('3. Ce qui a été testé'!G5:G40,"ROUGE*")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF('3. Tests à réaliser'!F5:F6,"À FAIRE*")</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1838,8 +1766,8 @@
         <v>83</v>
       </c>
       <c r="I7" s="12" t="str">
-        <f aca="false">IF(G7=H7,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G7=H7,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>84</v>
@@ -1871,8 +1799,8 @@
         <v>89</v>
       </c>
       <c r="I8" s="12" t="str">
-        <f aca="false">IF(G8=H8,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G8=H8,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>84</v>
@@ -1904,8 +1832,8 @@
         <v>94</v>
       </c>
       <c r="I9" s="12" t="str">
-        <f aca="false">IF(G9=H9,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G9=H9,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J9" s="12" t="s">
         <v>95</v>
@@ -1937,7 +1865,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="12" t="str">
-        <f aca="false">IF(G10=H10,"Oui","Non, mais testée (onglet 3)")</f>
+        <f aca="false">IF(G10=H10,"Oui","Non (à tester : onglet 3)")</f>
         <v>Oui</v>
       </c>
       <c r="J10" s="12" t="s">
@@ -1970,8 +1898,8 @@
         <v>105</v>
       </c>
       <c r="I11" s="12" t="str">
-        <f aca="false">IF(G11=H11,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G11=H11,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>95</v>
@@ -2003,8 +1931,8 @@
         <v>109</v>
       </c>
       <c r="I12" s="12" t="str">
-        <f aca="false">IF(G12=H12,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G12=H12,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>95</v>
@@ -2036,8 +1964,8 @@
         <v>113</v>
       </c>
       <c r="I13" s="12" t="str">
-        <f aca="false">IF(G13=H13,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G13=H13,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>101</v>
@@ -2069,8 +1997,8 @@
         <v>117</v>
       </c>
       <c r="I14" s="12" t="str">
-        <f aca="false">IF(G14=H14,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G14=H14,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>95</v>
@@ -2102,8 +2030,8 @@
         <v>122</v>
       </c>
       <c r="I15" s="12" t="str">
-        <f aca="false">IF(G15=H15,"Oui","Non, mais testée (onglet 3)")</f>
-        <v>Non, mais testée (onglet 3)</v>
+        <f aca="false">IF(G15=H15,"Oui","Non (à tester : onglet 3)")</f>
+        <v>Non (à tester : onglet 3)</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>101</v>
@@ -2135,7 +2063,7 @@
         <v>126</v>
       </c>
       <c r="I16" s="12" t="str">
-        <f aca="false">IF(G16=H16,"Oui","Non, mais testée (onglet 3)")</f>
+        <f aca="false">IF(G16=H16,"Oui","Non (à tester : onglet 3)")</f>
         <v>Oui</v>
       </c>
       <c r="J16" s="12" t="s">
@@ -2168,7 +2096,7 @@
         <v>130</v>
       </c>
       <c r="I17" s="12" t="str">
-        <f aca="false">IF(G17=H17,"Oui","Non, mais testée (onglet 3)")</f>
+        <f aca="false">IF(G17=H17,"Oui","Non (à tester : onglet 3)")</f>
         <v>Oui</v>
       </c>
       <c r="J17" s="12" t="s">
@@ -2302,7 +2230,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>3</v>
       </c>
@@ -2353,7 +2281,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>6</v>
       </c>
@@ -2367,7 +2295,7 @@
         <v>155</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2418,7 +2346,7 @@
         <v>164</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2519,16 +2447,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2561,13 +2489,10 @@
         <v>180</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H4" s="11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>182</v>
       </c>
@@ -2589,267 +2514,79 @@
       <c r="G5" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="H5" s="12" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="B6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C6" s="12" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="B7" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="C7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="12" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="12" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>217</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G14">
+  <conditionalFormatting sqref="F5:F7">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(G5,4)="VERT"</formula>
+      <formula>LEFT(F5,4)="VERT"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEFT(G5,6)="ORANGE"</formula>
+      <formula>LEFT(F5,6)="ORANGE"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>LEFT(G5,5)="ROUGE"</formula>
+      <formula>LEFT(F5,5)="ROUGE"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>LEFT(G5,9)="À REMPLIR"</formula>
+      <formula>LEFT(F5,9)="À REMPLIR"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>LEFT($F5,7)="À FAIRE"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2885,27 +2622,27 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2913,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>64</v>
@@ -2933,10 +2670,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>42</v>
@@ -2953,10 +2690,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>42</v>
@@ -2973,10 +2710,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>42</v>
@@ -2993,10 +2730,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>42</v>
@@ -3013,10 +2750,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>42</v>
@@ -3033,10 +2770,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>42</v>
@@ -3048,15 +2785,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>42</v>
@@ -3073,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>64</v>
@@ -3132,35 +2869,35 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>42</v>
@@ -3188,7 +2925,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>73</v>
@@ -3392,13 +3129,13 @@
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>251</v>
+        <v>64</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>42</v>
@@ -3409,13 +3146,13 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>42</v>
@@ -3426,7 +3163,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3493,221 +3230,221 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx
+++ b/docs/recapitulatif/Dependances_versions_VISU_PTBG.xlsx
@@ -424,7 +424,7 @@
     <t xml:space="preserve">Toutes ces versions existent pour Windows 11 64 bits et pour SLES 15 SP7 64 bits (fichiers d'installation vérifiés, sans compilation). Le 32 bits n'est pas une cible du projet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Le PC Spyder n'a pas les versions de référence (on ne peut rien y installer) ; l'outil s'y lance. Les tests automatiques diront si ces versions conviennent : voir l'onglet 3.</t>
+    <t xml:space="preserve">Le PC Spyder n'a pas les versions de référence (on ne peut rien y installer) ; l'outil s'y lance et les tests automatiques passent avec ces versions : voir l'onglet 3.</t>
   </si>
   <si>
     <t xml:space="preserve">Que se passe-t-il si on passe à une autre version de Python, d'une bibliothèque ou de système, et que faut-il faire ?</t>
@@ -517,10 +517,10 @@
     <t xml:space="preserve">Le PC Spyder garde numpy 2.2.0 et matplotlib 3.9.3</t>
   </si>
   <si>
-    <t xml:space="preserve">L'outil s'y lance et ouvre un fichier du projet. Ces versions acceptent Python 3.11.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lancer les tests sur le PC pour le confirmer (onglet 3).</t>
+    <t xml:space="preserve">L'outil s'y lance et ouvre un fichier du projet ; les tests passent avec ces versions (30/10/2026, onglet 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rien. Relancer les tests si Spyder est mis à jour.</t>
   </si>
   <si>
     <t xml:space="preserve">Le PC Spyder passe aux versions de référence (numpy 2.4.6, matplotlib 3.10.9)</t>
@@ -577,10 +577,10 @@
     <t xml:space="preserve">1. PC Windows 11 / Spyder 6 (poste de l'alternance)</t>
   </si>
   <si>
-    <t xml:space="preserve">À FAIRE — l'outil se lance et ouvre un fichier du projet (30/10/2026) ; les tests restent à lancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dans la console Spyder : import sys, puis %cd &lt;dossier de l'outil&gt;, puis !"{sys.executable}" -m unittest discover -s tests -v. Résultat attendu : « OK » à la fin.</t>
+    <t xml:space="preserve">VERT — FAIT le 30/10/2026 : l'outil se lance et ouvre un fichier du projet ; 145 tests lancés, 144 OK. Le seul en erreur cherchait le Word de la spécification, absent du dossier (corrigé : ce test est maintenant sauté sans le Word)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la console Spyder : import sys, puis %cd &lt;dossier de l'outil&gt;, puis !"{sys.executable}" -m unittest discover -s tests -v. Résultat attendu : « OK » à la fin (« OK (skipped=1) » si le Word de la spécification n'est pas dans docs/specification/).</t>
   </si>
   <si>
     <t xml:space="preserve">2. VM Linux SLES 15 SP7 fournie par l'entreprise</t>
@@ -709,7 +709,7 @@
     <t xml:space="preserve">Résultat de l'essai</t>
   </si>
   <si>
-    <t xml:space="preserve">Outil lancé, fichier du projet ouvert : OK ; tests à lancer</t>
+    <t xml:space="preserve">Outil lancé, fichier du projet ouvert : OK. Tests : 144 sur 145 OK (le dernier cherchait le Word de la spécification, absent ; corrigé). Essai de 15 min (COMPATIBILITE_OS.md § 5) : à faire</t>
   </si>
   <si>
     <t xml:space="preserve">Date du relevé</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B39" s="10" t="n">
         <f aca="false">COUNTIF('3. Tests à réaliser'!F5:F6,"À FAIRE*")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1766,8 +1766,8 @@
         <v>83</v>
       </c>
       <c r="I7" s="12" t="str">
-        <f aca="false">IF(G7=H7,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G7=H7,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>84</v>
@@ -1799,8 +1799,8 @@
         <v>89</v>
       </c>
       <c r="I8" s="12" t="str">
-        <f aca="false">IF(G8=H8,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G8=H8,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>84</v>
@@ -1832,8 +1832,8 @@
         <v>94</v>
       </c>
       <c r="I9" s="12" t="str">
-        <f aca="false">IF(G9=H9,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G9=H9,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J9" s="12" t="s">
         <v>95</v>
@@ -1865,7 +1865,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="12" t="str">
-        <f aca="false">IF(G10=H10,"Oui","Non (à tester : onglet 3)")</f>
+        <f aca="false">IF(G10=H10,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
         <v>Oui</v>
       </c>
       <c r="J10" s="12" t="s">
@@ -1898,8 +1898,8 @@
         <v>105</v>
       </c>
       <c r="I11" s="12" t="str">
-        <f aca="false">IF(G11=H11,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G11=H11,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>95</v>
@@ -1931,8 +1931,8 @@
         <v>109</v>
       </c>
       <c r="I12" s="12" t="str">
-        <f aca="false">IF(G12=H12,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G12=H12,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>95</v>
@@ -1964,8 +1964,8 @@
         <v>113</v>
       </c>
       <c r="I13" s="12" t="str">
-        <f aca="false">IF(G13=H13,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G13=H13,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>101</v>
@@ -1997,8 +1997,8 @@
         <v>117</v>
       </c>
       <c r="I14" s="12" t="str">
-        <f aca="false">IF(G14=H14,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G14=H14,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>95</v>
@@ -2030,8 +2030,8 @@
         <v>122</v>
       </c>
       <c r="I15" s="12" t="str">
-        <f aca="false">IF(G15=H15,"Oui","Non (à tester : onglet 3)")</f>
-        <v>Non (à tester : onglet 3)</v>
+        <f aca="false">IF(G15=H15,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
+        <v>Non (tests OK sur le PC : onglet 3)</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>101</v>
@@ -2063,7 +2063,7 @@
         <v>126</v>
       </c>
       <c r="I16" s="12" t="str">
-        <f aca="false">IF(G16=H16,"Oui","Non (à tester : onglet 3)")</f>
+        <f aca="false">IF(G16=H16,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
         <v>Oui</v>
       </c>
       <c r="J16" s="12" t="s">
@@ -2096,7 +2096,7 @@
         <v>130</v>
       </c>
       <c r="I17" s="12" t="str">
-        <f aca="false">IF(G17=H17,"Oui","Non (à tester : onglet 3)")</f>
+        <f aca="false">IF(G17=H17,"Oui","Non (tests OK sur le PC : onglet 3)")</f>
         <v>Oui</v>
       </c>
       <c r="J17" s="12" t="s">
@@ -2346,7 +2346,7 @@
         <v>164</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2492,7 +2492,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>182</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>226</v>
       </c>
